--- a/output/pdf_financials_xlsx/RVX.xlsx
+++ b/output/pdf_financials_xlsx/RVX.xlsx
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>4.164</v>
+        <v>-0</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0.117</v>
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2.082</v>
+        <v>-2.082</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-18.782</v>
@@ -1957,7 +1957,7 @@
         <v>-27.578099</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.082</v>
+        <v>-2.082</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-18.782</v>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-52.05</v>
+        <v>52.05</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>-64.765517</v>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-200</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>0.6268416822930619</v>
@@ -6459,7 +6459,7 @@
         <v>-27.578099</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>2.082</v>
+        <v>-2.082</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>-18.782</v>
@@ -37351,7 +37351,7 @@
         </is>
       </c>
       <c r="G298" s="5" t="n">
-        <v>2.082</v>
+        <v>-2.082</v>
       </c>
       <c r="H298" s="5" t="n">
         <v>-18.782</v>

--- a/output/pdf_financials_xlsx/RVX.xlsx
+++ b/output/pdf_financials_xlsx/RVX.xlsx
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.078</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.082</v>
+        <v>-2.004</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>18.665</v>
+        <v>18.736</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.801</v>
+        <v>-1.723</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>19.248</v>
+        <v>19.319</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -2680,43 +2680,43 @@
         <v>7.562</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>17.413</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>16.211</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>28.109</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.355</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.121</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>7.689</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.099</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="35">
@@ -2796,43 +2796,43 @@
         <v>7.562</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>17.413</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>16.211</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>28.109</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.355</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.121</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>7.689</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.099</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="37">
@@ -3492,43 +3492,43 @@
         <v>0.1</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>19.098</v>
+        <v>1.685</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.048</v>
+        <v>0.458</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>18.749</v>
+        <v>2.538</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>36.481</v>
+        <v>8.372</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>5.654</v>
+        <v>4.299</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>4.044</v>
+        <v>3.923</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>10.64</v>
+        <v>2.951</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>3.184</v>
+        <v>3.18</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.953</v>
+        <v>2.947</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>2.888</v>
+        <v>2.848</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>1.538</v>
+        <v>1.439</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>1.606</v>
+        <v>1.498</v>
       </c>
     </row>
     <row r="49">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -18871,7 +18871,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -63761,7 +63761,7 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">

--- a/output/pdf_financials_xlsx/RVX.xlsx
+++ b/output/pdf_financials_xlsx/RVX.xlsx
@@ -1287,13 +1287,13 @@
         <v>-0</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>-0</v>
+        <v>-10.519</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>-0</v>
+        <v>-3.021</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>-0</v>
+        <v>-2.692</v>
       </c>
     </row>
     <row r="14">
@@ -2263,13 +2263,13 @@
         <v>3.592</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>16.726</v>
+        <v>27.245</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>7.621</v>
+        <v>10.642</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>7.756</v>
+        <v>10.448</v>
       </c>
     </row>
     <row r="28">
@@ -2395,13 +2395,13 @@
         <v>4.599</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>17.442</v>
+        <v>27.961</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>7.969</v>
+        <v>10.99</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>8.186</v>
+        <v>10.878</v>
       </c>
     </row>
     <row r="30">
@@ -7226,7 +7226,7 @@
         <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.323</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>0</v>
@@ -39610,7 +39610,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
@@ -45552,7 +45556,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D381" t="inlineStr"/>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E381" t="inlineStr">
         <is>
           <t>-</t>
@@ -47805,7 +47813,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E404" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/RVX.xlsx
+++ b/output/pdf_financials_xlsx/RVX.xlsx
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>110.29</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>-37.737</v>
@@ -1771,10 +1771,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G20" s="3" t="n">
+        <v>55.104</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>-18.323</v>
@@ -1962,13 +1960,11 @@
       <c r="E23" s="3" t="n">
         <v>-18.782</v>
       </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F23" s="3" t="n">
+        <v>-43.355</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-55.186</v>
+        <v>55.104</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>-18.323</v>
@@ -1985,10 +1981,8 @@
       <c r="L23" s="3" t="n">
         <v>-162.798</v>
       </c>
-      <c r="M23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M23" s="3" t="n">
+        <v>118.025</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>-24.771</v>
@@ -2166,7 +2160,7 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>79.97971</v>
+        <v>-79.86087000000001</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>-83.28636400000001</v>
@@ -2524,7 +2518,7 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0</v>
+        <v>-199.851411589896</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>194.3803440815906</v>
@@ -4623,25 +4617,25 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>1.744</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>1.022</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.576</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>1.045</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.476</v>
       </c>
       <c r="J67" s="3" t="n">
         <v>0</v>
@@ -4684,22 +4678,22 @@
         <v>3.985845</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>4.11</v>
+        <v>5.854</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>3.28</v>
+        <v>4.302</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>3.327</v>
+        <v>4.497</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>1.571</v>
+        <v>2.147</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>1.936</v>
+        <v>2.981</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>4.942</v>
+        <v>5.418</v>
       </c>
       <c r="J68" s="3" t="n">
         <v>12.155</v>
@@ -4827,13 +4821,13 @@
         <v>0</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.711</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.632</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.437</v>
       </c>
       <c r="P70" s="3" t="n">
         <v>0</v>
@@ -4885,13 +4879,13 @@
         <v>0</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.711</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.632</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.437</v>
       </c>
       <c r="P71" s="3" t="n">
         <v>0</v>
@@ -5090,22 +5084,22 @@
         <v>28.199155</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>8.097</v>
+        <v>6.353</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>6.35</v>
+        <v>5.328</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>20.016</v>
+        <v>18.846</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>4.202</v>
+        <v>3.626</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>20.41</v>
+        <v>19.365</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>9.667999999999999</v>
+        <v>9.192</v>
       </c>
       <c r="J75" s="3" t="n">
         <v>57.581</v>
@@ -5117,13 +5111,13 @@
         <v>78.419</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>20.813</v>
+        <v>20.102</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>8.717000000000001</v>
+        <v>8.085000000000001</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>8.638999999999999</v>
+        <v>8.202</v>
       </c>
       <c r="P75" s="3" t="n">
         <v>12.368</v>
@@ -5421,15 +5415,13 @@
         </is>
       </c>
       <c r="M80" s="3" t="n">
-        <v>-0.01555091090591465</v>
+        <v>-0.02664087846269029</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>-0.007382662435276432</v>
-      </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.01793886754635043</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>-0.00737167051837857</v>
       </c>
       <c r="P80" s="1" t="inlineStr">
         <is>
@@ -6464,13 +6456,11 @@
       <c r="E99" s="3" t="n">
         <v>-18.782</v>
       </c>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F99" s="3" t="n">
+        <v>-43.355</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>-55.186</v>
+        <v>55.104</v>
       </c>
       <c r="H99" s="3" t="n">
         <v>-18.323</v>
@@ -6487,10 +6477,8 @@
       <c r="L99" s="3" t="n">
         <v>-162.798</v>
       </c>
-      <c r="M99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M99" s="3" t="n">
+        <v>118.025</v>
       </c>
       <c r="N99" s="3" t="n">
         <v>-24.771</v>
@@ -13082,7 +13070,11 @@
           <t>Lease liabilities 9</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -34256,7 +34248,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -38816,7 +38812,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -39212,7 +39212,11 @@
           <t>Income taxes, current and deferred tax recovery</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
